--- a/data/buoys.xlsx
+++ b/data/buoys.xlsx
@@ -1,18 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inana\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1E546E-5767-4ADB-A1FB-11C75EC7F064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ブイ一覧" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="選択肢" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="ブイ一覧" sheetId="1" r:id="rId1"/>
+    <sheet name="選択肢" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -21,12 +37,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="B5" authorId="0">
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -34,7 +50,7 @@
             <rFont val="Noto Sans CJK SC"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">この地点の集落名を入れてください（いただいた座標とリンクのみ入力済み）</t>
+          <t>この地点の集落名を入れてください（いただいた座標とリンクのみ入力済み）</t>
         </r>
       </text>
     </comment>
@@ -43,45 +59,43 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <r>
       <rPr>
-        <b val="true"/>
+        <b/>
         <sz val="13"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Floating </t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
+        <b/>
         <sz val="13"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">ブイ一覧（集落と</t>
+      <t>ブイ一覧（集落と</t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
+        <b/>
         <sz val="13"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
-      <t xml:space="preserve">YouTube</t>
+      <t>YouTube</t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
+        <b/>
         <sz val="13"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">動画の紐づけ）</t>
+      <t>動画の紐づけ）</t>
     </r>
   </si>
   <si>
@@ -92,17 +106,16 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">黄色の列だけ入力・修正してください。</t>
+      <t>黄色の列だけ入力・修正してください。</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF555555"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t>1</t>
     </r>
     <r>
       <rPr>
@@ -111,17 +124,16 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">行が</t>
+      <t>行が</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF555555"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t>1</t>
     </r>
     <r>
       <rPr>
@@ -130,17 +142,16 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">つのブイです。「表示」を</t>
+      <t>つのブイです。「表示」を</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF555555"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
-      <t xml:space="preserve">×</t>
+      <t>×</t>
     </r>
     <r>
       <rPr>
@@ -149,73 +160,69 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">にすると、その行は作品に出ません。「チェック」列は自動で判定します。</t>
+      <t>にすると、その行は作品に出ません。「チェック」列は自動で判定します。</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">集落名</t>
-  </si>
-  <si>
-    <t xml:space="preserve">集落形態</t>
-  </si>
-  <si>
-    <t xml:space="preserve">北緯</t>
-  </si>
-  <si>
-    <t xml:space="preserve">東経</t>
+    <t>No</t>
+  </si>
+  <si>
+    <t>集落名</t>
+  </si>
+  <si>
+    <t>集落形態</t>
+  </si>
+  <si>
+    <t>北緯</t>
+  </si>
+  <si>
+    <t>東経</t>
   </si>
   <si>
     <r>
       <rPr>
-        <b val="true"/>
+        <b/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
-      <t xml:space="preserve">YouTube</t>
+      <t>YouTube</t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
+        <b/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">リンク</t>
+      <t>リンク</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">表示</t>
-  </si>
-  <si>
-    <t xml:space="preserve">備考</t>
-  </si>
-  <si>
-    <t xml:space="preserve">チェック</t>
-  </si>
-  <si>
-    <t xml:space="preserve">メモ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（集落名を入力）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">湖岸集落</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://youtu.be/jjFq9K2AmFY?si=ufqVeeX_aVCmUB1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">○</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最初のブイ（試作で設置済み）</t>
+    <t>表示</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>チェック</t>
+  </si>
+  <si>
+    <t>メモ</t>
+  </si>
+  <si>
+    <t>湖岸集落</t>
+  </si>
+  <si>
+    <t>https://youtu.be/jjFq9K2AmFY?si=ufqVeeX_aVCmUB1L</t>
+  </si>
+  <si>
+    <t>○</t>
+  </si>
+  <si>
+    <t>最初のブイ（試作で設置済み）</t>
   </si>
   <si>
     <r>
@@ -224,16 +231,15 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">北緯・東経は度の小数（</t>
+      <t>北緯・東経は度の小数（</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Google</t>
+      <t>Google</t>
     </r>
     <r>
       <rPr>
@@ -241,7 +247,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">マップや地理院地図でコピーした値）。</t>
+      <t>マップや地理院地図でコピーした値）。</t>
     </r>
   </si>
   <si>
@@ -251,16 +257,15 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">チェックの範囲は琵琶湖周辺（北緯</t>
+      <t>チェックの範囲は琵琶湖周辺（北緯</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
-      <t xml:space="preserve">34.85</t>
+      <t>34.85</t>
     </r>
     <r>
       <rPr>
@@ -268,16 +273,15 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">〜</t>
+      <t>〜</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
-      <t xml:space="preserve">35.6</t>
+      <t>35.6</t>
     </r>
     <r>
       <rPr>
@@ -285,16 +289,15 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">、東経</t>
+      <t>、東経</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
-      <t xml:space="preserve">135.8</t>
+      <t>135.8</t>
     </r>
     <r>
       <rPr>
@@ -302,16 +305,15 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">〜</t>
+      <t>〜</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
-      <t xml:space="preserve">136.35</t>
+      <t>136.35</t>
     </r>
     <r>
       <rPr>
@@ -319,11 +321,11 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）。</t>
+      <t>）。</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">位置が陸側に入る場合、作品では近くの水面へ自動でずらします。</t>
+    <t>位置が陸側に入る場合、作品では近くの水面へ自動でずらします。</t>
   </si>
   <si>
     <r>
@@ -332,16 +334,15 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">行が足りなければ下へ続けて追加できます（</t>
+      <t>行が足りなければ下へ続けて追加できます（</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
-      <t xml:space="preserve">No</t>
+      <t>No</t>
     </r>
     <r>
       <rPr>
@@ -349,50 +350,87 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">・チェック列もコピー）。</t>
+      <t>・チェック列もコピー）。</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">集落形態の選択肢（自由に追加・変更できます）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">漁村</t>
-  </si>
-  <si>
-    <t xml:space="preserve">港町</t>
-  </si>
-  <si>
-    <t xml:space="preserve">内湖集落</t>
-  </si>
-  <si>
-    <t xml:space="preserve">水郷集落</t>
-  </si>
-  <si>
-    <t xml:space="preserve">島の集落</t>
-  </si>
-  <si>
-    <t xml:space="preserve">川沿い集落</t>
-  </si>
-  <si>
-    <t xml:space="preserve">門前町</t>
-  </si>
-  <si>
-    <t xml:space="preserve">城下町</t>
-  </si>
-  <si>
-    <t xml:space="preserve">宿場町</t>
-  </si>
-  <si>
-    <t xml:space="preserve">その他</t>
+    <t>集落形態の選択肢（自由に追加・変更できます）</t>
+  </si>
+  <si>
+    <t>漁村</t>
+  </si>
+  <si>
+    <t>港町</t>
+  </si>
+  <si>
+    <t>内湖集落</t>
+  </si>
+  <si>
+    <t>水郷集落</t>
+  </si>
+  <si>
+    <t>島の集落</t>
+  </si>
+  <si>
+    <t>川沿い集落</t>
+  </si>
+  <si>
+    <t>門前町</t>
+  </si>
+  <si>
+    <t>城下町</t>
+  </si>
+  <si>
+    <t>宿場町</t>
+  </si>
+  <si>
+    <t>その他</t>
+  </si>
+  <si>
+    <t>浜知内</t>
+    <rPh sb="0" eb="1">
+      <t>ハマ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>チナイ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>https://youtu.be/1q7oIvVAhCM?si=JCi4PO1bhpbcEzYL</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>https://youtu.be/UecpbkkTf38?si=8kMHi1T8pavBmZiB</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>海津</t>
+    <rPh sb="0" eb="2">
+      <t>ウミツ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>https://youtu.be/3BciUsr56RY?si=USmvr0XFcvHuJpDf</t>
+  </si>
+  <si>
+    <t>https://youtu.be/RPWBh-YWeXI?si=yzinTdO_bGTATR_z</t>
+  </si>
+  <si>
+    <t>大浦</t>
+    <rPh sb="0" eb="2">
+      <t>オオウラ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.000000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.000000"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -403,29 +441,13 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="13"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="13"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
@@ -440,26 +462,24 @@
       <sz val="9"/>
       <color rgb="FF555555"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
@@ -467,8 +487,7 @@
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -480,8 +499,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -491,13 +509,31 @@
     <font>
       <sz val="9"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="4">
@@ -521,14 +557,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -538,93 +574,36 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -683,47 +662,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF2F4A6D"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -731,12 +726,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -765,7 +760,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -786,7 +781,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -837,7 +832,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -855,43 +850,42 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K104"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="58.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:11" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:11">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -923,114 +917,162 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+    <row r="5" spans="1:11">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="8">
+        <v>35.444669900000001</v>
+      </c>
+      <c r="E5" s="8">
+        <v>136.05537000000001</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="8" t="n">
-        <v>35.4471669138861</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>136.054454537507</v>
-      </c>
-      <c r="F5" s="9" t="s">
+      <c r="G5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="H5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="6" t="str">
+        <f t="shared" ref="I5:I36" si="0">IF(AND(D5="",E5=""),"",IF(AND(ISNUMBER(D5),ISNUMBER(E5),D5&gt;=34.85,D5&lt;=35.6,E5&gt;=135.8,E5&lt;=136.35),IF(F5="","リンク未入力","OK"),"位置を確認"))</f>
+        <v>OK</v>
+      </c>
+      <c r="K5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="6" t="str">
-        <f aca="false">IF(AND(D5="",E5=""),"",IF(AND(ISNUMBER(D5),ISNUMBER(E5),D5&gt;=34.85,D5&lt;=35.6,E5&gt;=135.8,E5&lt;=136.35),IF(F5="","リンク未入力","OK"),"位置を確認"))</f>
-        <v>OK</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="10"/>
+      <c r="B6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="8">
+        <v>35.448160999999999</v>
+      </c>
+      <c r="E6" s="8">
+        <v>136.05856199999999</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="H6" s="7"/>
       <c r="I6" s="6" t="str">
-        <f aca="false">IF(AND(D6="",E6=""),"",IF(AND(ISNUMBER(D6),ISNUMBER(E6),D6&gt;=34.85,D6&lt;=35.6,E6&gt;=135.8,E6&lt;=136.35),IF(F6="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
+        <f t="shared" si="0"/>
+        <v>OK</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="10"/>
+      <c r="B7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="8">
+        <v>35.462569999999999</v>
+      </c>
+      <c r="E7" s="8">
+        <v>136.07225399999999</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="H7" s="7"/>
       <c r="I7" s="6" t="str">
-        <f aca="false">IF(AND(D7="",E7=""),"",IF(AND(ISNUMBER(D7),ISNUMBER(E7),D7&gt;=34.85,D7&lt;=35.6,E7&gt;=135.8,E7&lt;=136.35),IF(F7="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
+        <f t="shared" si="0"/>
+        <v>OK</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="10"/>
+      <c r="B8" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="8">
+        <v>35.462850000000003</v>
+      </c>
+      <c r="E8" s="8">
+        <v>136.07309100000001</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="H8" s="7"/>
       <c r="I8" s="6" t="str">
-        <f aca="false">IF(AND(D8="",E8=""),"",IF(AND(ISNUMBER(D8),ISNUMBER(E8),D8&gt;=34.85,D8&lt;=35.6,E8&gt;=135.8,E8&lt;=136.35),IF(F8="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
+        <f t="shared" si="0"/>
+        <v>OK</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="10"/>
+      <c r="B9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="8">
+        <v>35.484994999999998</v>
+      </c>
+      <c r="E9" s="8">
+        <v>136.121621</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="H9" s="7"/>
       <c r="I9" s="6" t="str">
-        <f aca="false">IF(AND(D9="",E9=""),"",IF(AND(ISNUMBER(D9),ISNUMBER(E9),D9&gt;=34.85,D9&lt;=35.6,E9&gt;=135.8,E9&lt;=136.35),IF(F9="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="6">
         <v>6</v>
       </c>
       <c r="B10" s="7"/>
@@ -1041,12 +1083,12 @@
       <c r="G10" s="10"/>
       <c r="H10" s="7"/>
       <c r="I10" s="6" t="str">
-        <f aca="false">IF(AND(D10="",E10=""),"",IF(AND(ISNUMBER(D10),ISNUMBER(E10),D10&gt;=34.85,D10&lt;=35.6,E10&gt;=135.8,E10&lt;=136.35),IF(F10="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="6">
         <v>7</v>
       </c>
       <c r="B11" s="7"/>
@@ -1057,12 +1099,12 @@
       <c r="G11" s="10"/>
       <c r="H11" s="7"/>
       <c r="I11" s="6" t="str">
-        <f aca="false">IF(AND(D11="",E11=""),"",IF(AND(ISNUMBER(D11),ISNUMBER(E11),D11&gt;=34.85,D11&lt;=35.6,E11&gt;=135.8,E11&lt;=136.35),IF(F11="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="6">
         <v>8</v>
       </c>
       <c r="B12" s="7"/>
@@ -1073,12 +1115,12 @@
       <c r="G12" s="10"/>
       <c r="H12" s="7"/>
       <c r="I12" s="6" t="str">
-        <f aca="false">IF(AND(D12="",E12=""),"",IF(AND(ISNUMBER(D12),ISNUMBER(E12),D12&gt;=34.85,D12&lt;=35.6,E12&gt;=135.8,E12&lt;=136.35),IF(F12="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="6">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
@@ -1089,12 +1131,12 @@
       <c r="G13" s="10"/>
       <c r="H13" s="7"/>
       <c r="I13" s="6" t="str">
-        <f aca="false">IF(AND(D13="",E13=""),"",IF(AND(ISNUMBER(D13),ISNUMBER(E13),D13&gt;=34.85,D13&lt;=35.6,E13&gt;=135.8,E13&lt;=136.35),IF(F13="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="6">
         <v>10</v>
       </c>
       <c r="B14" s="7"/>
@@ -1105,12 +1147,12 @@
       <c r="G14" s="10"/>
       <c r="H14" s="7"/>
       <c r="I14" s="6" t="str">
-        <f aca="false">IF(AND(D14="",E14=""),"",IF(AND(ISNUMBER(D14),ISNUMBER(E14),D14&gt;=34.85,D14&lt;=35.6,E14&gt;=135.8,E14&lt;=136.35),IF(F14="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="6">
         <v>11</v>
       </c>
       <c r="B15" s="7"/>
@@ -1121,12 +1163,12 @@
       <c r="G15" s="10"/>
       <c r="H15" s="7"/>
       <c r="I15" s="6" t="str">
-        <f aca="false">IF(AND(D15="",E15=""),"",IF(AND(ISNUMBER(D15),ISNUMBER(E15),D15&gt;=34.85,D15&lt;=35.6,E15&gt;=135.8,E15&lt;=136.35),IF(F15="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="6">
         <v>12</v>
       </c>
       <c r="B16" s="7"/>
@@ -1137,12 +1179,12 @@
       <c r="G16" s="10"/>
       <c r="H16" s="7"/>
       <c r="I16" s="6" t="str">
-        <f aca="false">IF(AND(D16="",E16=""),"",IF(AND(ISNUMBER(D16),ISNUMBER(E16),D16&gt;=34.85,D16&lt;=35.6,E16&gt;=135.8,E16&lt;=136.35),IF(F16="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6">
         <v>13</v>
       </c>
       <c r="B17" s="7"/>
@@ -1153,12 +1195,12 @@
       <c r="G17" s="10"/>
       <c r="H17" s="7"/>
       <c r="I17" s="6" t="str">
-        <f aca="false">IF(AND(D17="",E17=""),"",IF(AND(ISNUMBER(D17),ISNUMBER(E17),D17&gt;=34.85,D17&lt;=35.6,E17&gt;=135.8,E17&lt;=136.35),IF(F17="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="6">
         <v>14</v>
       </c>
       <c r="B18" s="7"/>
@@ -1169,12 +1211,12 @@
       <c r="G18" s="10"/>
       <c r="H18" s="7"/>
       <c r="I18" s="6" t="str">
-        <f aca="false">IF(AND(D18="",E18=""),"",IF(AND(ISNUMBER(D18),ISNUMBER(E18),D18&gt;=34.85,D18&lt;=35.6,E18&gt;=135.8,E18&lt;=136.35),IF(F18="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="6">
         <v>15</v>
       </c>
       <c r="B19" s="7"/>
@@ -1185,12 +1227,12 @@
       <c r="G19" s="10"/>
       <c r="H19" s="7"/>
       <c r="I19" s="6" t="str">
-        <f aca="false">IF(AND(D19="",E19=""),"",IF(AND(ISNUMBER(D19),ISNUMBER(E19),D19&gt;=34.85,D19&lt;=35.6,E19&gt;=135.8,E19&lt;=136.35),IF(F19="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="6">
         <v>16</v>
       </c>
       <c r="B20" s="7"/>
@@ -1201,12 +1243,12 @@
       <c r="G20" s="10"/>
       <c r="H20" s="7"/>
       <c r="I20" s="6" t="str">
-        <f aca="false">IF(AND(D20="",E20=""),"",IF(AND(ISNUMBER(D20),ISNUMBER(E20),D20&gt;=34.85,D20&lt;=35.6,E20&gt;=135.8,E20&lt;=136.35),IF(F20="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="6">
         <v>17</v>
       </c>
       <c r="B21" s="7"/>
@@ -1217,12 +1259,12 @@
       <c r="G21" s="10"/>
       <c r="H21" s="7"/>
       <c r="I21" s="6" t="str">
-        <f aca="false">IF(AND(D21="",E21=""),"",IF(AND(ISNUMBER(D21),ISNUMBER(E21),D21&gt;=34.85,D21&lt;=35.6,E21&gt;=135.8,E21&lt;=136.35),IF(F21="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="6">
         <v>18</v>
       </c>
       <c r="B22" s="7"/>
@@ -1233,12 +1275,12 @@
       <c r="G22" s="10"/>
       <c r="H22" s="7"/>
       <c r="I22" s="6" t="str">
-        <f aca="false">IF(AND(D22="",E22=""),"",IF(AND(ISNUMBER(D22),ISNUMBER(E22),D22&gt;=34.85,D22&lt;=35.6,E22&gt;=135.8,E22&lt;=136.35),IF(F22="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="6">
         <v>19</v>
       </c>
       <c r="B23" s="7"/>
@@ -1249,12 +1291,12 @@
       <c r="G23" s="10"/>
       <c r="H23" s="7"/>
       <c r="I23" s="6" t="str">
-        <f aca="false">IF(AND(D23="",E23=""),"",IF(AND(ISNUMBER(D23),ISNUMBER(E23),D23&gt;=34.85,D23&lt;=35.6,E23&gt;=135.8,E23&lt;=136.35),IF(F23="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="6">
         <v>20</v>
       </c>
       <c r="B24" s="7"/>
@@ -1265,12 +1307,12 @@
       <c r="G24" s="10"/>
       <c r="H24" s="7"/>
       <c r="I24" s="6" t="str">
-        <f aca="false">IF(AND(D24="",E24=""),"",IF(AND(ISNUMBER(D24),ISNUMBER(E24),D24&gt;=34.85,D24&lt;=35.6,E24&gt;=135.8,E24&lt;=136.35),IF(F24="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="6">
         <v>21</v>
       </c>
       <c r="B25" s="7"/>
@@ -1281,12 +1323,12 @@
       <c r="G25" s="10"/>
       <c r="H25" s="7"/>
       <c r="I25" s="6" t="str">
-        <f aca="false">IF(AND(D25="",E25=""),"",IF(AND(ISNUMBER(D25),ISNUMBER(E25),D25&gt;=34.85,D25&lt;=35.6,E25&gt;=135.8,E25&lt;=136.35),IF(F25="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="6">
         <v>22</v>
       </c>
       <c r="B26" s="7"/>
@@ -1297,12 +1339,12 @@
       <c r="G26" s="10"/>
       <c r="H26" s="7"/>
       <c r="I26" s="6" t="str">
-        <f aca="false">IF(AND(D26="",E26=""),"",IF(AND(ISNUMBER(D26),ISNUMBER(E26),D26&gt;=34.85,D26&lt;=35.6,E26&gt;=135.8,E26&lt;=136.35),IF(F26="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="6">
         <v>23</v>
       </c>
       <c r="B27" s="7"/>
@@ -1313,12 +1355,12 @@
       <c r="G27" s="10"/>
       <c r="H27" s="7"/>
       <c r="I27" s="6" t="str">
-        <f aca="false">IF(AND(D27="",E27=""),"",IF(AND(ISNUMBER(D27),ISNUMBER(E27),D27&gt;=34.85,D27&lt;=35.6,E27&gt;=135.8,E27&lt;=136.35),IF(F27="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="6">
         <v>24</v>
       </c>
       <c r="B28" s="7"/>
@@ -1329,12 +1371,12 @@
       <c r="G28" s="10"/>
       <c r="H28" s="7"/>
       <c r="I28" s="6" t="str">
-        <f aca="false">IF(AND(D28="",E28=""),"",IF(AND(ISNUMBER(D28),ISNUMBER(E28),D28&gt;=34.85,D28&lt;=35.6,E28&gt;=135.8,E28&lt;=136.35),IF(F28="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="6">
         <v>25</v>
       </c>
       <c r="B29" s="7"/>
@@ -1345,12 +1387,12 @@
       <c r="G29" s="10"/>
       <c r="H29" s="7"/>
       <c r="I29" s="6" t="str">
-        <f aca="false">IF(AND(D29="",E29=""),"",IF(AND(ISNUMBER(D29),ISNUMBER(E29),D29&gt;=34.85,D29&lt;=35.6,E29&gt;=135.8,E29&lt;=136.35),IF(F29="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="6">
         <v>26</v>
       </c>
       <c r="B30" s="7"/>
@@ -1361,12 +1403,12 @@
       <c r="G30" s="10"/>
       <c r="H30" s="7"/>
       <c r="I30" s="6" t="str">
-        <f aca="false">IF(AND(D30="",E30=""),"",IF(AND(ISNUMBER(D30),ISNUMBER(E30),D30&gt;=34.85,D30&lt;=35.6,E30&gt;=135.8,E30&lt;=136.35),IF(F30="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="6">
         <v>27</v>
       </c>
       <c r="B31" s="7"/>
@@ -1377,12 +1419,12 @@
       <c r="G31" s="10"/>
       <c r="H31" s="7"/>
       <c r="I31" s="6" t="str">
-        <f aca="false">IF(AND(D31="",E31=""),"",IF(AND(ISNUMBER(D31),ISNUMBER(E31),D31&gt;=34.85,D31&lt;=35.6,E31&gt;=135.8,E31&lt;=136.35),IF(F31="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="6">
         <v>28</v>
       </c>
       <c r="B32" s="7"/>
@@ -1393,12 +1435,12 @@
       <c r="G32" s="10"/>
       <c r="H32" s="7"/>
       <c r="I32" s="6" t="str">
-        <f aca="false">IF(AND(D32="",E32=""),"",IF(AND(ISNUMBER(D32),ISNUMBER(E32),D32&gt;=34.85,D32&lt;=35.6,E32&gt;=135.8,E32&lt;=136.35),IF(F32="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="6">
         <v>29</v>
       </c>
       <c r="B33" s="7"/>
@@ -1409,12 +1451,12 @@
       <c r="G33" s="10"/>
       <c r="H33" s="7"/>
       <c r="I33" s="6" t="str">
-        <f aca="false">IF(AND(D33="",E33=""),"",IF(AND(ISNUMBER(D33),ISNUMBER(E33),D33&gt;=34.85,D33&lt;=35.6,E33&gt;=135.8,E33&lt;=136.35),IF(F33="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6">
         <v>30</v>
       </c>
       <c r="B34" s="7"/>
@@ -1425,12 +1467,12 @@
       <c r="G34" s="10"/>
       <c r="H34" s="7"/>
       <c r="I34" s="6" t="str">
-        <f aca="false">IF(AND(D34="",E34=""),"",IF(AND(ISNUMBER(D34),ISNUMBER(E34),D34&gt;=34.85,D34&lt;=35.6,E34&gt;=135.8,E34&lt;=136.35),IF(F34="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="6">
         <v>31</v>
       </c>
       <c r="B35" s="7"/>
@@ -1441,12 +1483,12 @@
       <c r="G35" s="10"/>
       <c r="H35" s="7"/>
       <c r="I35" s="6" t="str">
-        <f aca="false">IF(AND(D35="",E35=""),"",IF(AND(ISNUMBER(D35),ISNUMBER(E35),D35&gt;=34.85,D35&lt;=35.6,E35&gt;=135.8,E35&lt;=136.35),IF(F35="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="6">
         <v>32</v>
       </c>
       <c r="B36" s="7"/>
@@ -1457,12 +1499,12 @@
       <c r="G36" s="10"/>
       <c r="H36" s="7"/>
       <c r="I36" s="6" t="str">
-        <f aca="false">IF(AND(D36="",E36=""),"",IF(AND(ISNUMBER(D36),ISNUMBER(E36),D36&gt;=34.85,D36&lt;=35.6,E36&gt;=135.8,E36&lt;=136.35),IF(F36="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="n">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="6">
         <v>33</v>
       </c>
       <c r="B37" s="7"/>
@@ -1473,12 +1515,12 @@
       <c r="G37" s="10"/>
       <c r="H37" s="7"/>
       <c r="I37" s="6" t="str">
-        <f aca="false">IF(AND(D37="",E37=""),"",IF(AND(ISNUMBER(D37),ISNUMBER(E37),D37&gt;=34.85,D37&lt;=35.6,E37&gt;=135.8,E37&lt;=136.35),IF(F37="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="n">
+        <f t="shared" ref="I37:I68" si="1">IF(AND(D37="",E37=""),"",IF(AND(ISNUMBER(D37),ISNUMBER(E37),D37&gt;=34.85,D37&lt;=35.6,E37&gt;=135.8,E37&lt;=136.35),IF(F37="","リンク未入力","OK"),"位置を確認"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="6">
         <v>34</v>
       </c>
       <c r="B38" s="7"/>
@@ -1489,12 +1531,12 @@
       <c r="G38" s="10"/>
       <c r="H38" s="7"/>
       <c r="I38" s="6" t="str">
-        <f aca="false">IF(AND(D38="",E38=""),"",IF(AND(ISNUMBER(D38),ISNUMBER(E38),D38&gt;=34.85,D38&lt;=35.6,E38&gt;=135.8,E38&lt;=136.35),IF(F38="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="6">
         <v>35</v>
       </c>
       <c r="B39" s="7"/>
@@ -1505,12 +1547,12 @@
       <c r="G39" s="10"/>
       <c r="H39" s="7"/>
       <c r="I39" s="6" t="str">
-        <f aca="false">IF(AND(D39="",E39=""),"",IF(AND(ISNUMBER(D39),ISNUMBER(E39),D39&gt;=34.85,D39&lt;=35.6,E39&gt;=135.8,E39&lt;=136.35),IF(F39="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="6">
         <v>36</v>
       </c>
       <c r="B40" s="7"/>
@@ -1521,12 +1563,12 @@
       <c r="G40" s="10"/>
       <c r="H40" s="7"/>
       <c r="I40" s="6" t="str">
-        <f aca="false">IF(AND(D40="",E40=""),"",IF(AND(ISNUMBER(D40),ISNUMBER(E40),D40&gt;=34.85,D40&lt;=35.6,E40&gt;=135.8,E40&lt;=136.35),IF(F40="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="6">
         <v>37</v>
       </c>
       <c r="B41" s="7"/>
@@ -1537,12 +1579,12 @@
       <c r="G41" s="10"/>
       <c r="H41" s="7"/>
       <c r="I41" s="6" t="str">
-        <f aca="false">IF(AND(D41="",E41=""),"",IF(AND(ISNUMBER(D41),ISNUMBER(E41),D41&gt;=34.85,D41&lt;=35.6,E41&gt;=135.8,E41&lt;=136.35),IF(F41="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="6">
         <v>38</v>
       </c>
       <c r="B42" s="7"/>
@@ -1553,12 +1595,12 @@
       <c r="G42" s="10"/>
       <c r="H42" s="7"/>
       <c r="I42" s="6" t="str">
-        <f aca="false">IF(AND(D42="",E42=""),"",IF(AND(ISNUMBER(D42),ISNUMBER(E42),D42&gt;=34.85,D42&lt;=35.6,E42&gt;=135.8,E42&lt;=136.35),IF(F42="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="6">
         <v>39</v>
       </c>
       <c r="B43" s="7"/>
@@ -1569,12 +1611,12 @@
       <c r="G43" s="10"/>
       <c r="H43" s="7"/>
       <c r="I43" s="6" t="str">
-        <f aca="false">IF(AND(D43="",E43=""),"",IF(AND(ISNUMBER(D43),ISNUMBER(E43),D43&gt;=34.85,D43&lt;=35.6,E43&gt;=135.8,E43&lt;=136.35),IF(F43="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="6">
         <v>40</v>
       </c>
       <c r="B44" s="7"/>
@@ -1585,12 +1627,12 @@
       <c r="G44" s="10"/>
       <c r="H44" s="7"/>
       <c r="I44" s="6" t="str">
-        <f aca="false">IF(AND(D44="",E44=""),"",IF(AND(ISNUMBER(D44),ISNUMBER(E44),D44&gt;=34.85,D44&lt;=35.6,E44&gt;=135.8,E44&lt;=136.35),IF(F44="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="6">
         <v>41</v>
       </c>
       <c r="B45" s="7"/>
@@ -1601,12 +1643,12 @@
       <c r="G45" s="10"/>
       <c r="H45" s="7"/>
       <c r="I45" s="6" t="str">
-        <f aca="false">IF(AND(D45="",E45=""),"",IF(AND(ISNUMBER(D45),ISNUMBER(E45),D45&gt;=34.85,D45&lt;=35.6,E45&gt;=135.8,E45&lt;=136.35),IF(F45="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="6">
         <v>42</v>
       </c>
       <c r="B46" s="7"/>
@@ -1617,12 +1659,12 @@
       <c r="G46" s="10"/>
       <c r="H46" s="7"/>
       <c r="I46" s="6" t="str">
-        <f aca="false">IF(AND(D46="",E46=""),"",IF(AND(ISNUMBER(D46),ISNUMBER(E46),D46&gt;=34.85,D46&lt;=35.6,E46&gt;=135.8,E46&lt;=136.35),IF(F46="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="6">
         <v>43</v>
       </c>
       <c r="B47" s="7"/>
@@ -1633,12 +1675,12 @@
       <c r="G47" s="10"/>
       <c r="H47" s="7"/>
       <c r="I47" s="6" t="str">
-        <f aca="false">IF(AND(D47="",E47=""),"",IF(AND(ISNUMBER(D47),ISNUMBER(E47),D47&gt;=34.85,D47&lt;=35.6,E47&gt;=135.8,E47&lt;=136.35),IF(F47="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="6">
         <v>44</v>
       </c>
       <c r="B48" s="7"/>
@@ -1649,12 +1691,12 @@
       <c r="G48" s="10"/>
       <c r="H48" s="7"/>
       <c r="I48" s="6" t="str">
-        <f aca="false">IF(AND(D48="",E48=""),"",IF(AND(ISNUMBER(D48),ISNUMBER(E48),D48&gt;=34.85,D48&lt;=35.6,E48&gt;=135.8,E48&lt;=136.35),IF(F48="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="6">
         <v>45</v>
       </c>
       <c r="B49" s="7"/>
@@ -1665,12 +1707,12 @@
       <c r="G49" s="10"/>
       <c r="H49" s="7"/>
       <c r="I49" s="6" t="str">
-        <f aca="false">IF(AND(D49="",E49=""),"",IF(AND(ISNUMBER(D49),ISNUMBER(E49),D49&gt;=34.85,D49&lt;=35.6,E49&gt;=135.8,E49&lt;=136.35),IF(F49="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="6">
         <v>46</v>
       </c>
       <c r="B50" s="7"/>
@@ -1681,12 +1723,12 @@
       <c r="G50" s="10"/>
       <c r="H50" s="7"/>
       <c r="I50" s="6" t="str">
-        <f aca="false">IF(AND(D50="",E50=""),"",IF(AND(ISNUMBER(D50),ISNUMBER(E50),D50&gt;=34.85,D50&lt;=35.6,E50&gt;=135.8,E50&lt;=136.35),IF(F50="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="6">
         <v>47</v>
       </c>
       <c r="B51" s="7"/>
@@ -1697,12 +1739,12 @@
       <c r="G51" s="10"/>
       <c r="H51" s="7"/>
       <c r="I51" s="6" t="str">
-        <f aca="false">IF(AND(D51="",E51=""),"",IF(AND(ISNUMBER(D51),ISNUMBER(E51),D51&gt;=34.85,D51&lt;=35.6,E51&gt;=135.8,E51&lt;=136.35),IF(F51="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="6">
         <v>48</v>
       </c>
       <c r="B52" s="7"/>
@@ -1713,12 +1755,12 @@
       <c r="G52" s="10"/>
       <c r="H52" s="7"/>
       <c r="I52" s="6" t="str">
-        <f aca="false">IF(AND(D52="",E52=""),"",IF(AND(ISNUMBER(D52),ISNUMBER(E52),D52&gt;=34.85,D52&lt;=35.6,E52&gt;=135.8,E52&lt;=136.35),IF(F52="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="6">
         <v>49</v>
       </c>
       <c r="B53" s="7"/>
@@ -1729,12 +1771,12 @@
       <c r="G53" s="10"/>
       <c r="H53" s="7"/>
       <c r="I53" s="6" t="str">
-        <f aca="false">IF(AND(D53="",E53=""),"",IF(AND(ISNUMBER(D53),ISNUMBER(E53),D53&gt;=34.85,D53&lt;=35.6,E53&gt;=135.8,E53&lt;=136.35),IF(F53="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="6">
         <v>50</v>
       </c>
       <c r="B54" s="7"/>
@@ -1745,12 +1787,12 @@
       <c r="G54" s="10"/>
       <c r="H54" s="7"/>
       <c r="I54" s="6" t="str">
-        <f aca="false">IF(AND(D54="",E54=""),"",IF(AND(ISNUMBER(D54),ISNUMBER(E54),D54&gt;=34.85,D54&lt;=35.6,E54&gt;=135.8,E54&lt;=136.35),IF(F54="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="6">
         <v>51</v>
       </c>
       <c r="B55" s="7"/>
@@ -1761,12 +1803,12 @@
       <c r="G55" s="10"/>
       <c r="H55" s="7"/>
       <c r="I55" s="6" t="str">
-        <f aca="false">IF(AND(D55="",E55=""),"",IF(AND(ISNUMBER(D55),ISNUMBER(E55),D55&gt;=34.85,D55&lt;=35.6,E55&gt;=135.8,E55&lt;=136.35),IF(F55="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="6">
         <v>52</v>
       </c>
       <c r="B56" s="7"/>
@@ -1777,12 +1819,12 @@
       <c r="G56" s="10"/>
       <c r="H56" s="7"/>
       <c r="I56" s="6" t="str">
-        <f aca="false">IF(AND(D56="",E56=""),"",IF(AND(ISNUMBER(D56),ISNUMBER(E56),D56&gt;=34.85,D56&lt;=35.6,E56&gt;=135.8,E56&lt;=136.35),IF(F56="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="6">
         <v>53</v>
       </c>
       <c r="B57" s="7"/>
@@ -1793,12 +1835,12 @@
       <c r="G57" s="10"/>
       <c r="H57" s="7"/>
       <c r="I57" s="6" t="str">
-        <f aca="false">IF(AND(D57="",E57=""),"",IF(AND(ISNUMBER(D57),ISNUMBER(E57),D57&gt;=34.85,D57&lt;=35.6,E57&gt;=135.8,E57&lt;=136.35),IF(F57="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="6">
         <v>54</v>
       </c>
       <c r="B58" s="7"/>
@@ -1809,12 +1851,12 @@
       <c r="G58" s="10"/>
       <c r="H58" s="7"/>
       <c r="I58" s="6" t="str">
-        <f aca="false">IF(AND(D58="",E58=""),"",IF(AND(ISNUMBER(D58),ISNUMBER(E58),D58&gt;=34.85,D58&lt;=35.6,E58&gt;=135.8,E58&lt;=136.35),IF(F58="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="6">
         <v>55</v>
       </c>
       <c r="B59" s="7"/>
@@ -1825,12 +1867,12 @@
       <c r="G59" s="10"/>
       <c r="H59" s="7"/>
       <c r="I59" s="6" t="str">
-        <f aca="false">IF(AND(D59="",E59=""),"",IF(AND(ISNUMBER(D59),ISNUMBER(E59),D59&gt;=34.85,D59&lt;=35.6,E59&gt;=135.8,E59&lt;=136.35),IF(F59="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="6">
         <v>56</v>
       </c>
       <c r="B60" s="7"/>
@@ -1841,12 +1883,12 @@
       <c r="G60" s="10"/>
       <c r="H60" s="7"/>
       <c r="I60" s="6" t="str">
-        <f aca="false">IF(AND(D60="",E60=""),"",IF(AND(ISNUMBER(D60),ISNUMBER(E60),D60&gt;=34.85,D60&lt;=35.6,E60&gt;=135.8,E60&lt;=136.35),IF(F60="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="6">
         <v>57</v>
       </c>
       <c r="B61" s="7"/>
@@ -1857,12 +1899,12 @@
       <c r="G61" s="10"/>
       <c r="H61" s="7"/>
       <c r="I61" s="6" t="str">
-        <f aca="false">IF(AND(D61="",E61=""),"",IF(AND(ISNUMBER(D61),ISNUMBER(E61),D61&gt;=34.85,D61&lt;=35.6,E61&gt;=135.8,E61&lt;=136.35),IF(F61="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="6">
         <v>58</v>
       </c>
       <c r="B62" s="7"/>
@@ -1873,12 +1915,12 @@
       <c r="G62" s="10"/>
       <c r="H62" s="7"/>
       <c r="I62" s="6" t="str">
-        <f aca="false">IF(AND(D62="",E62=""),"",IF(AND(ISNUMBER(D62),ISNUMBER(E62),D62&gt;=34.85,D62&lt;=35.6,E62&gt;=135.8,E62&lt;=136.35),IF(F62="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="6">
         <v>59</v>
       </c>
       <c r="B63" s="7"/>
@@ -1889,12 +1931,12 @@
       <c r="G63" s="10"/>
       <c r="H63" s="7"/>
       <c r="I63" s="6" t="str">
-        <f aca="false">IF(AND(D63="",E63=""),"",IF(AND(ISNUMBER(D63),ISNUMBER(E63),D63&gt;=34.85,D63&lt;=35.6,E63&gt;=135.8,E63&lt;=136.35),IF(F63="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" s="6">
         <v>60</v>
       </c>
       <c r="B64" s="7"/>
@@ -1905,12 +1947,12 @@
       <c r="G64" s="10"/>
       <c r="H64" s="7"/>
       <c r="I64" s="6" t="str">
-        <f aca="false">IF(AND(D64="",E64=""),"",IF(AND(ISNUMBER(D64),ISNUMBER(E64),D64&gt;=34.85,D64&lt;=35.6,E64&gt;=135.8,E64&lt;=136.35),IF(F64="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" s="6">
         <v>61</v>
       </c>
       <c r="B65" s="7"/>
@@ -1921,12 +1963,12 @@
       <c r="G65" s="10"/>
       <c r="H65" s="7"/>
       <c r="I65" s="6" t="str">
-        <f aca="false">IF(AND(D65="",E65=""),"",IF(AND(ISNUMBER(D65),ISNUMBER(E65),D65&gt;=34.85,D65&lt;=35.6,E65&gt;=135.8,E65&lt;=136.35),IF(F65="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" s="6">
         <v>62</v>
       </c>
       <c r="B66" s="7"/>
@@ -1937,12 +1979,12 @@
       <c r="G66" s="10"/>
       <c r="H66" s="7"/>
       <c r="I66" s="6" t="str">
-        <f aca="false">IF(AND(D66="",E66=""),"",IF(AND(ISNUMBER(D66),ISNUMBER(E66),D66&gt;=34.85,D66&lt;=35.6,E66&gt;=135.8,E66&lt;=136.35),IF(F66="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" s="6">
         <v>63</v>
       </c>
       <c r="B67" s="7"/>
@@ -1953,12 +1995,12 @@
       <c r="G67" s="10"/>
       <c r="H67" s="7"/>
       <c r="I67" s="6" t="str">
-        <f aca="false">IF(AND(D67="",E67=""),"",IF(AND(ISNUMBER(D67),ISNUMBER(E67),D67&gt;=34.85,D67&lt;=35.6,E67&gt;=135.8,E67&lt;=136.35),IF(F67="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" s="6">
         <v>64</v>
       </c>
       <c r="B68" s="7"/>
@@ -1969,12 +2011,12 @@
       <c r="G68" s="10"/>
       <c r="H68" s="7"/>
       <c r="I68" s="6" t="str">
-        <f aca="false">IF(AND(D68="",E68=""),"",IF(AND(ISNUMBER(D68),ISNUMBER(E68),D68&gt;=34.85,D68&lt;=35.6,E68&gt;=135.8,E68&lt;=136.35),IF(F68="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="6" t="n">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" s="6">
         <v>65</v>
       </c>
       <c r="B69" s="7"/>
@@ -1985,12 +2027,12 @@
       <c r="G69" s="10"/>
       <c r="H69" s="7"/>
       <c r="I69" s="6" t="str">
-        <f aca="false">IF(AND(D69="",E69=""),"",IF(AND(ISNUMBER(D69),ISNUMBER(E69),D69&gt;=34.85,D69&lt;=35.6,E69&gt;=135.8,E69&lt;=136.35),IF(F69="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="6" t="n">
+        <f t="shared" ref="I69:I104" si="2">IF(AND(D69="",E69=""),"",IF(AND(ISNUMBER(D69),ISNUMBER(E69),D69&gt;=34.85,D69&lt;=35.6,E69&gt;=135.8,E69&lt;=136.35),IF(F69="","リンク未入力","OK"),"位置を確認"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" s="6">
         <v>66</v>
       </c>
       <c r="B70" s="7"/>
@@ -2001,12 +2043,12 @@
       <c r="G70" s="10"/>
       <c r="H70" s="7"/>
       <c r="I70" s="6" t="str">
-        <f aca="false">IF(AND(D70="",E70=""),"",IF(AND(ISNUMBER(D70),ISNUMBER(E70),D70&gt;=34.85,D70&lt;=35.6,E70&gt;=135.8,E70&lt;=136.35),IF(F70="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" s="6">
         <v>67</v>
       </c>
       <c r="B71" s="7"/>
@@ -2017,12 +2059,12 @@
       <c r="G71" s="10"/>
       <c r="H71" s="7"/>
       <c r="I71" s="6" t="str">
-        <f aca="false">IF(AND(D71="",E71=""),"",IF(AND(ISNUMBER(D71),ISNUMBER(E71),D71&gt;=34.85,D71&lt;=35.6,E71&gt;=135.8,E71&lt;=136.35),IF(F71="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" s="6">
         <v>68</v>
       </c>
       <c r="B72" s="7"/>
@@ -2033,12 +2075,12 @@
       <c r="G72" s="10"/>
       <c r="H72" s="7"/>
       <c r="I72" s="6" t="str">
-        <f aca="false">IF(AND(D72="",E72=""),"",IF(AND(ISNUMBER(D72),ISNUMBER(E72),D72&gt;=34.85,D72&lt;=35.6,E72&gt;=135.8,E72&lt;=136.35),IF(F72="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" s="6">
         <v>69</v>
       </c>
       <c r="B73" s="7"/>
@@ -2049,12 +2091,12 @@
       <c r="G73" s="10"/>
       <c r="H73" s="7"/>
       <c r="I73" s="6" t="str">
-        <f aca="false">IF(AND(D73="",E73=""),"",IF(AND(ISNUMBER(D73),ISNUMBER(E73),D73&gt;=34.85,D73&lt;=35.6,E73&gt;=135.8,E73&lt;=136.35),IF(F73="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" s="6">
         <v>70</v>
       </c>
       <c r="B74" s="7"/>
@@ -2065,12 +2107,12 @@
       <c r="G74" s="10"/>
       <c r="H74" s="7"/>
       <c r="I74" s="6" t="str">
-        <f aca="false">IF(AND(D74="",E74=""),"",IF(AND(ISNUMBER(D74),ISNUMBER(E74),D74&gt;=34.85,D74&lt;=35.6,E74&gt;=135.8,E74&lt;=136.35),IF(F74="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" s="6">
         <v>71</v>
       </c>
       <c r="B75" s="7"/>
@@ -2081,12 +2123,12 @@
       <c r="G75" s="10"/>
       <c r="H75" s="7"/>
       <c r="I75" s="6" t="str">
-        <f aca="false">IF(AND(D75="",E75=""),"",IF(AND(ISNUMBER(D75),ISNUMBER(E75),D75&gt;=34.85,D75&lt;=35.6,E75&gt;=135.8,E75&lt;=136.35),IF(F75="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" s="6">
         <v>72</v>
       </c>
       <c r="B76" s="7"/>
@@ -2097,12 +2139,12 @@
       <c r="G76" s="10"/>
       <c r="H76" s="7"/>
       <c r="I76" s="6" t="str">
-        <f aca="false">IF(AND(D76="",E76=""),"",IF(AND(ISNUMBER(D76),ISNUMBER(E76),D76&gt;=34.85,D76&lt;=35.6,E76&gt;=135.8,E76&lt;=136.35),IF(F76="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" s="6">
         <v>73</v>
       </c>
       <c r="B77" s="7"/>
@@ -2113,12 +2155,12 @@
       <c r="G77" s="10"/>
       <c r="H77" s="7"/>
       <c r="I77" s="6" t="str">
-        <f aca="false">IF(AND(D77="",E77=""),"",IF(AND(ISNUMBER(D77),ISNUMBER(E77),D77&gt;=34.85,D77&lt;=35.6,E77&gt;=135.8,E77&lt;=136.35),IF(F77="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" s="6">
         <v>74</v>
       </c>
       <c r="B78" s="7"/>
@@ -2129,12 +2171,12 @@
       <c r="G78" s="10"/>
       <c r="H78" s="7"/>
       <c r="I78" s="6" t="str">
-        <f aca="false">IF(AND(D78="",E78=""),"",IF(AND(ISNUMBER(D78),ISNUMBER(E78),D78&gt;=34.85,D78&lt;=35.6,E78&gt;=135.8,E78&lt;=136.35),IF(F78="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" s="6">
         <v>75</v>
       </c>
       <c r="B79" s="7"/>
@@ -2145,12 +2187,12 @@
       <c r="G79" s="10"/>
       <c r="H79" s="7"/>
       <c r="I79" s="6" t="str">
-        <f aca="false">IF(AND(D79="",E79=""),"",IF(AND(ISNUMBER(D79),ISNUMBER(E79),D79&gt;=34.85,D79&lt;=35.6,E79&gt;=135.8,E79&lt;=136.35),IF(F79="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" s="6">
         <v>76</v>
       </c>
       <c r="B80" s="7"/>
@@ -2161,12 +2203,12 @@
       <c r="G80" s="10"/>
       <c r="H80" s="7"/>
       <c r="I80" s="6" t="str">
-        <f aca="false">IF(AND(D80="",E80=""),"",IF(AND(ISNUMBER(D80),ISNUMBER(E80),D80&gt;=34.85,D80&lt;=35.6,E80&gt;=135.8,E80&lt;=136.35),IF(F80="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" s="6">
         <v>77</v>
       </c>
       <c r="B81" s="7"/>
@@ -2177,12 +2219,12 @@
       <c r="G81" s="10"/>
       <c r="H81" s="7"/>
       <c r="I81" s="6" t="str">
-        <f aca="false">IF(AND(D81="",E81=""),"",IF(AND(ISNUMBER(D81),ISNUMBER(E81),D81&gt;=34.85,D81&lt;=35.6,E81&gt;=135.8,E81&lt;=136.35),IF(F81="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" s="6">
         <v>78</v>
       </c>
       <c r="B82" s="7"/>
@@ -2193,12 +2235,12 @@
       <c r="G82" s="10"/>
       <c r="H82" s="7"/>
       <c r="I82" s="6" t="str">
-        <f aca="false">IF(AND(D82="",E82=""),"",IF(AND(ISNUMBER(D82),ISNUMBER(E82),D82&gt;=34.85,D82&lt;=35.6,E82&gt;=135.8,E82&lt;=136.35),IF(F82="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" s="6">
         <v>79</v>
       </c>
       <c r="B83" s="7"/>
@@ -2209,12 +2251,12 @@
       <c r="G83" s="10"/>
       <c r="H83" s="7"/>
       <c r="I83" s="6" t="str">
-        <f aca="false">IF(AND(D83="",E83=""),"",IF(AND(ISNUMBER(D83),ISNUMBER(E83),D83&gt;=34.85,D83&lt;=35.6,E83&gt;=135.8,E83&lt;=136.35),IF(F83="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" s="6">
         <v>80</v>
       </c>
       <c r="B84" s="7"/>
@@ -2225,12 +2267,12 @@
       <c r="G84" s="10"/>
       <c r="H84" s="7"/>
       <c r="I84" s="6" t="str">
-        <f aca="false">IF(AND(D84="",E84=""),"",IF(AND(ISNUMBER(D84),ISNUMBER(E84),D84&gt;=34.85,D84&lt;=35.6,E84&gt;=135.8,E84&lt;=136.35),IF(F84="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" s="6">
         <v>81</v>
       </c>
       <c r="B85" s="7"/>
@@ -2241,12 +2283,12 @@
       <c r="G85" s="10"/>
       <c r="H85" s="7"/>
       <c r="I85" s="6" t="str">
-        <f aca="false">IF(AND(D85="",E85=""),"",IF(AND(ISNUMBER(D85),ISNUMBER(E85),D85&gt;=34.85,D85&lt;=35.6,E85&gt;=135.8,E85&lt;=136.35),IF(F85="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" s="6">
         <v>82</v>
       </c>
       <c r="B86" s="7"/>
@@ -2257,12 +2299,12 @@
       <c r="G86" s="10"/>
       <c r="H86" s="7"/>
       <c r="I86" s="6" t="str">
-        <f aca="false">IF(AND(D86="",E86=""),"",IF(AND(ISNUMBER(D86),ISNUMBER(E86),D86&gt;=34.85,D86&lt;=35.6,E86&gt;=135.8,E86&lt;=136.35),IF(F86="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" s="6">
         <v>83</v>
       </c>
       <c r="B87" s="7"/>
@@ -2273,12 +2315,12 @@
       <c r="G87" s="10"/>
       <c r="H87" s="7"/>
       <c r="I87" s="6" t="str">
-        <f aca="false">IF(AND(D87="",E87=""),"",IF(AND(ISNUMBER(D87),ISNUMBER(E87),D87&gt;=34.85,D87&lt;=35.6,E87&gt;=135.8,E87&lt;=136.35),IF(F87="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="6">
         <v>84</v>
       </c>
       <c r="B88" s="7"/>
@@ -2289,12 +2331,12 @@
       <c r="G88" s="10"/>
       <c r="H88" s="7"/>
       <c r="I88" s="6" t="str">
-        <f aca="false">IF(AND(D88="",E88=""),"",IF(AND(ISNUMBER(D88),ISNUMBER(E88),D88&gt;=34.85,D88&lt;=35.6,E88&gt;=135.8,E88&lt;=136.35),IF(F88="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" s="6">
         <v>85</v>
       </c>
       <c r="B89" s="7"/>
@@ -2305,12 +2347,12 @@
       <c r="G89" s="10"/>
       <c r="H89" s="7"/>
       <c r="I89" s="6" t="str">
-        <f aca="false">IF(AND(D89="",E89=""),"",IF(AND(ISNUMBER(D89),ISNUMBER(E89),D89&gt;=34.85,D89&lt;=35.6,E89&gt;=135.8,E89&lt;=136.35),IF(F89="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" s="6">
         <v>86</v>
       </c>
       <c r="B90" s="7"/>
@@ -2321,12 +2363,12 @@
       <c r="G90" s="10"/>
       <c r="H90" s="7"/>
       <c r="I90" s="6" t="str">
-        <f aca="false">IF(AND(D90="",E90=""),"",IF(AND(ISNUMBER(D90),ISNUMBER(E90),D90&gt;=34.85,D90&lt;=35.6,E90&gt;=135.8,E90&lt;=136.35),IF(F90="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" s="6">
         <v>87</v>
       </c>
       <c r="B91" s="7"/>
@@ -2337,12 +2379,12 @@
       <c r="G91" s="10"/>
       <c r="H91" s="7"/>
       <c r="I91" s="6" t="str">
-        <f aca="false">IF(AND(D91="",E91=""),"",IF(AND(ISNUMBER(D91),ISNUMBER(E91),D91&gt;=34.85,D91&lt;=35.6,E91&gt;=135.8,E91&lt;=136.35),IF(F91="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" s="6">
         <v>88</v>
       </c>
       <c r="B92" s="7"/>
@@ -2353,12 +2395,12 @@
       <c r="G92" s="10"/>
       <c r="H92" s="7"/>
       <c r="I92" s="6" t="str">
-        <f aca="false">IF(AND(D92="",E92=""),"",IF(AND(ISNUMBER(D92),ISNUMBER(E92),D92&gt;=34.85,D92&lt;=35.6,E92&gt;=135.8,E92&lt;=136.35),IF(F92="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" s="6">
         <v>89</v>
       </c>
       <c r="B93" s="7"/>
@@ -2369,12 +2411,12 @@
       <c r="G93" s="10"/>
       <c r="H93" s="7"/>
       <c r="I93" s="6" t="str">
-        <f aca="false">IF(AND(D93="",E93=""),"",IF(AND(ISNUMBER(D93),ISNUMBER(E93),D93&gt;=34.85,D93&lt;=35.6,E93&gt;=135.8,E93&lt;=136.35),IF(F93="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" s="6">
         <v>90</v>
       </c>
       <c r="B94" s="7"/>
@@ -2385,12 +2427,12 @@
       <c r="G94" s="10"/>
       <c r="H94" s="7"/>
       <c r="I94" s="6" t="str">
-        <f aca="false">IF(AND(D94="",E94=""),"",IF(AND(ISNUMBER(D94),ISNUMBER(E94),D94&gt;=34.85,D94&lt;=35.6,E94&gt;=135.8,E94&lt;=136.35),IF(F94="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" s="6">
         <v>91</v>
       </c>
       <c r="B95" s="7"/>
@@ -2401,12 +2443,12 @@
       <c r="G95" s="10"/>
       <c r="H95" s="7"/>
       <c r="I95" s="6" t="str">
-        <f aca="false">IF(AND(D95="",E95=""),"",IF(AND(ISNUMBER(D95),ISNUMBER(E95),D95&gt;=34.85,D95&lt;=35.6,E95&gt;=135.8,E95&lt;=136.35),IF(F95="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" s="6">
         <v>92</v>
       </c>
       <c r="B96" s="7"/>
@@ -2417,12 +2459,12 @@
       <c r="G96" s="10"/>
       <c r="H96" s="7"/>
       <c r="I96" s="6" t="str">
-        <f aca="false">IF(AND(D96="",E96=""),"",IF(AND(ISNUMBER(D96),ISNUMBER(E96),D96&gt;=34.85,D96&lt;=35.6,E96&gt;=135.8,E96&lt;=136.35),IF(F96="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" s="6">
         <v>93</v>
       </c>
       <c r="B97" s="7"/>
@@ -2433,12 +2475,12 @@
       <c r="G97" s="10"/>
       <c r="H97" s="7"/>
       <c r="I97" s="6" t="str">
-        <f aca="false">IF(AND(D97="",E97=""),"",IF(AND(ISNUMBER(D97),ISNUMBER(E97),D97&gt;=34.85,D97&lt;=35.6,E97&gt;=135.8,E97&lt;=136.35),IF(F97="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" s="6">
         <v>94</v>
       </c>
       <c r="B98" s="7"/>
@@ -2449,12 +2491,12 @@
       <c r="G98" s="10"/>
       <c r="H98" s="7"/>
       <c r="I98" s="6" t="str">
-        <f aca="false">IF(AND(D98="",E98=""),"",IF(AND(ISNUMBER(D98),ISNUMBER(E98),D98&gt;=34.85,D98&lt;=35.6,E98&gt;=135.8,E98&lt;=136.35),IF(F98="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" s="6">
         <v>95</v>
       </c>
       <c r="B99" s="7"/>
@@ -2465,12 +2507,12 @@
       <c r="G99" s="10"/>
       <c r="H99" s="7"/>
       <c r="I99" s="6" t="str">
-        <f aca="false">IF(AND(D99="",E99=""),"",IF(AND(ISNUMBER(D99),ISNUMBER(E99),D99&gt;=34.85,D99&lt;=35.6,E99&gt;=135.8,E99&lt;=136.35),IF(F99="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" s="6">
         <v>96</v>
       </c>
       <c r="B100" s="7"/>
@@ -2481,12 +2523,12 @@
       <c r="G100" s="10"/>
       <c r="H100" s="7"/>
       <c r="I100" s="6" t="str">
-        <f aca="false">IF(AND(D100="",E100=""),"",IF(AND(ISNUMBER(D100),ISNUMBER(E100),D100&gt;=34.85,D100&lt;=35.6,E100&gt;=135.8,E100&lt;=136.35),IF(F100="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" s="6">
         <v>97</v>
       </c>
       <c r="B101" s="7"/>
@@ -2497,12 +2539,12 @@
       <c r="G101" s="10"/>
       <c r="H101" s="7"/>
       <c r="I101" s="6" t="str">
-        <f aca="false">IF(AND(D101="",E101=""),"",IF(AND(ISNUMBER(D101),ISNUMBER(E101),D101&gt;=34.85,D101&lt;=35.6,E101&gt;=135.8,E101&lt;=136.35),IF(F101="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" s="6">
         <v>98</v>
       </c>
       <c r="B102" s="7"/>
@@ -2513,12 +2555,12 @@
       <c r="G102" s="10"/>
       <c r="H102" s="7"/>
       <c r="I102" s="6" t="str">
-        <f aca="false">IF(AND(D102="",E102=""),"",IF(AND(ISNUMBER(D102),ISNUMBER(E102),D102&gt;=34.85,D102&lt;=35.6,E102&gt;=135.8,E102&lt;=136.35),IF(F102="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" s="6">
         <v>99</v>
       </c>
       <c r="B103" s="7"/>
@@ -2529,12 +2571,12 @@
       <c r="G103" s="10"/>
       <c r="H103" s="7"/>
       <c r="I103" s="6" t="str">
-        <f aca="false">IF(AND(D103="",E103=""),"",IF(AND(ISNUMBER(D103),ISNUMBER(E103),D103&gt;=34.85,D103&lt;=35.6,E103&gt;=135.8,E103&lt;=136.35),IF(F103="","リンク未入力","OK"),"位置を確認"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="6" t="n">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" s="6">
         <v>100</v>
       </c>
       <c r="B104" s="7"/>
@@ -2545,118 +2587,118 @@
       <c r="G104" s="10"/>
       <c r="H104" s="7"/>
       <c r="I104" s="6" t="str">
-        <f aca="false">IF(AND(D104="",E104=""),"",IF(AND(ISNUMBER(D104),ISNUMBER(E104),D104&gt;=34.85,D104&lt;=35.6,E104&gt;=135.8,E104&lt;=136.35),IF(F104="","リンク未入力","OK"),"位置を確認"))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C5:C104" type="list">
-      <formula1>選択肢!$A$2:$A$40</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G104" type="list">
+  <phoneticPr fontId="15"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" sqref="G5:G104" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"○,×"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="度の小数（例 35.447167）で入力してください" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:D104" type="decimal">
+    <dataValidation type="decimal" allowBlank="1" error="度の小数（例 35.447167）で入力してください" sqref="D5:D104" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>34</formula1>
       <formula2>36</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="度の小数（例 35.447167）で入力してください" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E5:E104" type="decimal">
+    <dataValidation type="decimal" allowBlank="1" error="度の小数（例 35.447167）で入力してください" sqref="E5:E104" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>135</formula1>
       <formula2>137</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+          <x14:formula1>
+            <xm:f>選択肢!$A$2:$A$40</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>C5:C104</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A12"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:1">
       <c r="A1" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
+    <row r="4" spans="1:1">
+      <c r="A4" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
+    <row r="5" spans="1:1">
+      <c r="A5" s="12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+    <row r="6" spans="1:1">
+      <c r="A6" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+    <row r="7" spans="1:1">
+      <c r="A7" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+    <row r="8" spans="1:1">
+      <c r="A8" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+    <row r="9" spans="1:1">
+      <c r="A9" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+    <row r="10" spans="1:1">
+      <c r="A10" s="12" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+    <row r="11" spans="1:1">
+      <c r="A11" s="12" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
+    <row r="12" spans="1:1">
+      <c r="A12" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <phoneticPr fontId="15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/data/buoys.xlsx
+++ b/data/buoys.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inana\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1E546E-5767-4ADB-A1FB-11C75EC7F064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435E1347-B9B9-489E-8790-56C168718137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="49">
   <si>
     <r>
       <rPr>
@@ -422,6 +422,71 @@
     <rPh sb="0" eb="2">
       <t>オオウラ</t>
     </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>菅浦</t>
+    <rPh sb="0" eb="2">
+      <t>スガウラ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>https://youtu.be/KuxpeiXOm5A?si=TWLwF5i7osQL98zF</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>https://youtu.be/cxg_TUoD-Uc?si=exvsJGoimMebB4l_</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>月出</t>
+    <rPh sb="0" eb="2">
+      <t>ツキデ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>https://youtu.be/ZY6gUO0k0J4?si=IBHugHzqHOz3rlVO</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>塩津</t>
+    <rPh sb="0" eb="2">
+      <t>シオツ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>https://youtu.be/1aK3fGYMvKw?si=cHjH5d7C_L18Bh8J</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>https://youtu.be/pag9WEgjz1E?si=olEjCrr9BNBoxBoZ</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>飯浦</t>
+    <rPh sb="0" eb="1">
+      <t>メシ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ウラ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>山梨子</t>
+    <rPh sb="0" eb="2">
+      <t>ヤマナシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>https://youtu.be/tFQ_NWmhTrg?si=AD3k2vKpihTJxUIs</t>
     <phoneticPr fontId="15"/>
   </si>
 </sst>
@@ -1075,96 +1140,168 @@
       <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="10"/>
+      <c r="B10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="8">
+        <v>35.457949999999997</v>
+      </c>
+      <c r="E10" s="8">
+        <v>136.13903500000001</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="H10" s="7"/>
       <c r="I10" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>OK</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="10"/>
+      <c r="B11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="8">
+        <v>35.456040000000002</v>
+      </c>
+      <c r="E11" s="8">
+        <v>136.14292399999999</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="H11" s="7"/>
       <c r="I11" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>OK</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="10"/>
+      <c r="B12" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="8">
+        <v>35.495308999999999</v>
+      </c>
+      <c r="E12" s="8">
+        <v>136.16101800000001</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="H12" s="7"/>
       <c r="I12" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>OK</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="10"/>
+      <c r="B13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="8">
+        <v>35.512206999999997</v>
+      </c>
+      <c r="E13" s="8">
+        <v>136.16474099999999</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="H13" s="7"/>
       <c r="I13" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>OK</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="10"/>
+      <c r="B14" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="8">
+        <v>35.502569999999999</v>
+      </c>
+      <c r="E14" s="8">
+        <v>136.18234699999999</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="H14" s="7"/>
       <c r="I14" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>OK</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="6">
         <v>11</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="10"/>
+      <c r="B15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="8">
+        <v>35.496143000000004</v>
+      </c>
+      <c r="E15" s="8">
+        <v>136.18962300000001</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="H15" s="7"/>
       <c r="I15" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>OK</v>
       </c>
     </row>
     <row r="16" spans="1:11">

--- a/data/buoys.xlsx
+++ b/data/buoys.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inana\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435E1347-B9B9-489E-8790-56C168718137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E622C76-3F08-4D46-8CB7-68ED13385274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="55">
   <si>
     <r>
       <rPr>
@@ -487,6 +487,36 @@
   </si>
   <si>
     <t>https://youtu.be/tFQ_NWmhTrg?si=AD3k2vKpihTJxUIs</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>https://youtu.be/zXBxAdKKC1g?si=xvg8R6GwvDf05Kvk</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>片山</t>
+    <rPh sb="0" eb="2">
+      <t>カタヤマ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>https://youtu.be/fb8DIJxNSwM?si=TnK-Qp26e1AOG2wT</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>尾上</t>
+    <rPh sb="0" eb="2">
+      <t>オノウエ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>https://youtu.be/0A8pNpCq_Lw?si=ljvSDHyMREGWHgx1</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>https://youtu.be/jSQpETXCC40?si=RTUJtfseuhQZchTv</t>
     <phoneticPr fontId="15"/>
   </si>
 </sst>
@@ -993,10 +1023,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="8">
-        <v>35.444669900000001</v>
+        <v>35.444156</v>
       </c>
       <c r="E5" s="8">
-        <v>136.05537000000001</v>
+        <v>136.056241</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>13</v>
@@ -1026,10 +1056,10 @@
         <v>12</v>
       </c>
       <c r="D6" s="8">
-        <v>35.448160999999999</v>
+        <v>35.446438999999998</v>
       </c>
       <c r="E6" s="8">
-        <v>136.05856199999999</v>
+        <v>136.062465</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>32</v>
@@ -1057,10 +1087,10 @@
         <v>12</v>
       </c>
       <c r="D7" s="8">
-        <v>35.462569999999999</v>
+        <v>35.461269000000001</v>
       </c>
       <c r="E7" s="8">
-        <v>136.07225399999999</v>
+        <v>136.072577</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>33</v>
@@ -1088,10 +1118,10 @@
         <v>12</v>
       </c>
       <c r="D8" s="8">
-        <v>35.462850000000003</v>
+        <v>35.462380000000003</v>
       </c>
       <c r="E8" s="8">
-        <v>136.07309100000001</v>
+        <v>136.07379</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>35</v>
@@ -1119,10 +1149,10 @@
         <v>12</v>
       </c>
       <c r="D9" s="8">
-        <v>35.484994999999998</v>
+        <v>35.484785000000002</v>
       </c>
       <c r="E9" s="8">
-        <v>136.121621</v>
+        <v>136.12044800000001</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>36</v>
@@ -1147,10 +1177,10 @@
         <v>12</v>
       </c>
       <c r="D10" s="8">
-        <v>35.457949999999997</v>
+        <v>35.456246</v>
       </c>
       <c r="E10" s="8">
-        <v>136.13903500000001</v>
+        <v>136.13756100000001</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>39</v>
@@ -1175,10 +1205,10 @@
         <v>12</v>
       </c>
       <c r="D11" s="8">
-        <v>35.456040000000002</v>
+        <v>35.455925000000001</v>
       </c>
       <c r="E11" s="8">
-        <v>136.14292399999999</v>
+        <v>136.140885</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>40</v>
@@ -1203,10 +1233,10 @@
         <v>12</v>
       </c>
       <c r="D12" s="8">
-        <v>35.495308999999999</v>
+        <v>35.494526999999998</v>
       </c>
       <c r="E12" s="8">
-        <v>136.16101800000001</v>
+        <v>136.162925</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>42</v>
@@ -1231,10 +1261,10 @@
         <v>12</v>
       </c>
       <c r="D13" s="8">
-        <v>35.512206999999997</v>
+        <v>35.510984000000001</v>
       </c>
       <c r="E13" s="8">
-        <v>136.16474099999999</v>
+        <v>136.16490300000001</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>44</v>
@@ -1259,10 +1289,10 @@
         <v>12</v>
       </c>
       <c r="D14" s="8">
-        <v>35.502569999999999</v>
+        <v>35.501305000000002</v>
       </c>
       <c r="E14" s="8">
-        <v>136.18234699999999</v>
+        <v>136.18218899999999</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>45</v>
@@ -1287,10 +1317,10 @@
         <v>12</v>
       </c>
       <c r="D15" s="8">
-        <v>35.496143000000004</v>
+        <v>35.494821000000002</v>
       </c>
       <c r="E15" s="8">
-        <v>136.18962300000001</v>
+        <v>136.18656300000001</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>48</v>
@@ -1308,64 +1338,112 @@
       <c r="A16" s="6">
         <v>12</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="10"/>
+      <c r="B16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="8">
+        <v>35.459456000000003</v>
+      </c>
+      <c r="E16" s="8">
+        <v>136.19308799999999</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="H16" s="7"/>
       <c r="I16" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>OK</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="10"/>
+      <c r="B17" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="8">
+        <v>35.456817999999998</v>
+      </c>
+      <c r="E17" s="8">
+        <v>136.19376</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="H17" s="7"/>
       <c r="I17" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>OK</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6">
         <v>14</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="10"/>
+      <c r="B18" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="8">
+        <v>35.455371</v>
+      </c>
+      <c r="E18" s="8">
+        <v>136.186533</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="H18" s="7"/>
       <c r="I18" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>OK</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="10"/>
+      <c r="B19" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="8">
+        <v>35.455756000000001</v>
+      </c>
+      <c r="E19" s="8">
+        <v>136.18831</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="H19" s="7"/>
       <c r="I19" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>OK</v>
       </c>
     </row>
     <row r="20" spans="1:9">
